--- a/research/traditional_assets/database/data/slovenia/slovenia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_reinsurance.xlsx
@@ -588,49 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09279999999999999</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E2">
-        <v>0.148</v>
-      </c>
-      <c r="F2">
-        <v>0.035</v>
+        <v>0.16</v>
       </c>
       <c r="G2">
-        <v>0.1046150551450905</v>
+        <v>0.1746737841043891</v>
       </c>
       <c r="H2">
-        <v>0.1046150551450905</v>
+        <v>0.1746737841043891</v>
       </c>
       <c r="I2">
-        <v>0.1051504443730592</v>
+        <v>0.120699881376038</v>
       </c>
       <c r="J2">
-        <v>0.08539287679977739</v>
+        <v>0.0989646536952955</v>
       </c>
       <c r="K2">
-        <v>76.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="L2">
-        <v>0.08180747403362246</v>
+        <v>0.09489916963226572</v>
       </c>
       <c r="M2">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="N2">
-        <v>0.03125</v>
+        <v>0.061455525606469</v>
       </c>
       <c r="O2">
-        <v>0.200261780104712</v>
+        <v>0.35625</v>
       </c>
       <c r="P2">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q2">
-        <v>0.03125</v>
+        <v>0.061455525606469</v>
       </c>
       <c r="R2">
-        <v>0.200261780104712</v>
+        <v>0.35625</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>115.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V2">
-        <v>0.235906862745098</v>
+        <v>0.2692722371967655</v>
       </c>
       <c r="W2">
-        <v>0.1485803189420459</v>
+        <v>0.1121036959187248</v>
       </c>
       <c r="X2">
-        <v>0.101927978129102</v>
+        <v>0.1416959172781294</v>
       </c>
       <c r="Y2">
-        <v>0.04665234081294392</v>
+        <v>-0.02959222135940459</v>
       </c>
       <c r="Z2">
-        <v>2.035971223021583</v>
+        <v>1.219309347315133</v>
       </c>
       <c r="AA2">
-        <v>0.1738574398153741</v>
+        <v>0.1206685273044789</v>
       </c>
       <c r="AB2">
-        <v>0.08949329079043861</v>
+        <v>0.1251823828519256</v>
       </c>
       <c r="AC2">
-        <v>0.0843641490249355</v>
+        <v>-0.004513855547446752</v>
       </c>
       <c r="AD2">
-        <v>97.7</v>
+        <v>81.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>97.7</v>
+        <v>81.7</v>
       </c>
       <c r="AG2">
-        <v>-17.8</v>
+        <v>-18.2</v>
       </c>
       <c r="AH2">
-        <v>0.1663545036608207</v>
+        <v>0.1804727192401149</v>
       </c>
       <c r="AI2">
-        <v>0.1460388639760837</v>
+        <v>0.1735344095157179</v>
       </c>
       <c r="AJ2">
-        <v>-0.0377278507842306</v>
+        <v>-0.05158730158730159</v>
       </c>
       <c r="AK2">
-        <v>-0.03215898825654923</v>
+        <v>-0.04906983014289566</v>
       </c>
       <c r="AL2">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AM2">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AN2">
-        <v>0.9190968955785513</v>
+        <v>0.9294653014789533</v>
       </c>
       <c r="AO2">
-        <v>26.9041095890411</v>
+        <v>25.67823343848581</v>
       </c>
       <c r="AP2">
-        <v>-0.167450611476952</v>
+        <v>-0.2070534698521047</v>
       </c>
       <c r="AQ2">
-        <v>26.9041095890411</v>
+        <v>25.67823343848581</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09279999999999999</v>
+        <v>0.05980000000000001</v>
       </c>
       <c r="E3">
-        <v>0.148</v>
-      </c>
-      <c r="F3">
-        <v>0.035</v>
+        <v>0.16</v>
       </c>
       <c r="G3">
-        <v>0.1046150551450905</v>
+        <v>0.1746737841043891</v>
       </c>
       <c r="H3">
-        <v>0.1046150551450905</v>
+        <v>0.1746737841043891</v>
       </c>
       <c r="I3">
-        <v>0.1051504443730592</v>
+        <v>0.120699881376038</v>
       </c>
       <c r="J3">
-        <v>0.08539287679977739</v>
+        <v>0.0989646536952955</v>
       </c>
       <c r="K3">
-        <v>76.40000000000001</v>
+        <v>64</v>
       </c>
       <c r="L3">
-        <v>0.08180747403362246</v>
+        <v>0.09489916963226572</v>
       </c>
       <c r="M3">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="N3">
-        <v>0.03125</v>
+        <v>0.061455525606469</v>
       </c>
       <c r="O3">
-        <v>0.200261780104712</v>
+        <v>0.35625</v>
       </c>
       <c r="P3">
-        <v>15.3</v>
+        <v>22.8</v>
       </c>
       <c r="Q3">
-        <v>0.03125</v>
+        <v>0.061455525606469</v>
       </c>
       <c r="R3">
-        <v>0.200261780104712</v>
+        <v>0.35625</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>115.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="V3">
-        <v>0.235906862745098</v>
+        <v>0.2692722371967655</v>
       </c>
       <c r="W3">
-        <v>0.1485803189420459</v>
+        <v>0.1121036959187248</v>
       </c>
       <c r="X3">
-        <v>0.101927978129102</v>
+        <v>0.1416959172781294</v>
       </c>
       <c r="Y3">
-        <v>0.04665234081294392</v>
+        <v>-0.02959222135940459</v>
       </c>
       <c r="Z3">
-        <v>2.035971223021583</v>
+        <v>1.219309347315133</v>
       </c>
       <c r="AA3">
-        <v>0.1738574398153741</v>
+        <v>0.1206685273044789</v>
       </c>
       <c r="AB3">
-        <v>0.08949329079043861</v>
+        <v>0.1251823828519256</v>
       </c>
       <c r="AC3">
-        <v>0.0843641490249355</v>
+        <v>-0.004513855547446752</v>
       </c>
       <c r="AD3">
-        <v>97.7</v>
+        <v>81.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>97.7</v>
+        <v>81.7</v>
       </c>
       <c r="AG3">
-        <v>-17.8</v>
+        <v>-18.2</v>
       </c>
       <c r="AH3">
-        <v>0.1663545036608207</v>
+        <v>0.1804727192401149</v>
       </c>
       <c r="AI3">
-        <v>0.1460388639760837</v>
+        <v>0.1735344095157179</v>
       </c>
       <c r="AJ3">
-        <v>-0.0377278507842306</v>
+        <v>-0.05158730158730159</v>
       </c>
       <c r="AK3">
-        <v>-0.03215898825654923</v>
+        <v>-0.04906983014289566</v>
       </c>
       <c r="AL3">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AM3">
-        <v>3.65</v>
+        <v>3.17</v>
       </c>
       <c r="AN3">
-        <v>0.9190968955785513</v>
+        <v>0.9294653014789533</v>
       </c>
       <c r="AO3">
-        <v>26.9041095890411</v>
+        <v>25.67823343848581</v>
       </c>
       <c r="AP3">
-        <v>-0.167450611476952</v>
+        <v>-0.2070534698521047</v>
       </c>
       <c r="AQ3">
-        <v>26.9041095890411</v>
+        <v>25.67823343848581</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/slovenia/slovenia_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_reinsurance.xlsx
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05980000000000001</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="E2">
-        <v>0.16</v>
+        <v>0.121</v>
       </c>
       <c r="G2">
-        <v>0.1746737841043891</v>
+        <v>0.1165672326755392</v>
       </c>
       <c r="H2">
-        <v>0.1746737841043891</v>
+        <v>0.1165672326755392</v>
       </c>
       <c r="I2">
-        <v>0.120699881376038</v>
+        <v>0.111863240018357</v>
       </c>
       <c r="J2">
-        <v>0.0989646536952955</v>
+        <v>0.08915234463666036</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>73.7</v>
       </c>
       <c r="L2">
-        <v>0.09489916963226572</v>
+        <v>0.08455713630105553</v>
       </c>
       <c r="M2">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.061455525606469</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.35625</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.061455525606469</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.35625</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>0.2692722371967655</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0.1121036959187248</v>
+        <v>0.1896063802418318</v>
       </c>
       <c r="X2">
-        <v>0.1416959172781294</v>
+        <v>0.1170478436518125</v>
       </c>
       <c r="Y2">
-        <v>-0.02959222135940459</v>
+        <v>0.07255853659001923</v>
       </c>
       <c r="Z2">
-        <v>1.219309347315133</v>
+        <v>2.352496626180837</v>
       </c>
       <c r="AA2">
-        <v>0.1206685273044789</v>
+        <v>0.2097305899738547</v>
       </c>
       <c r="AB2">
-        <v>0.1251823828519256</v>
+        <v>0.1060832382678796</v>
       </c>
       <c r="AC2">
-        <v>-0.004513855547446752</v>
+        <v>0.1036473517059751</v>
       </c>
       <c r="AD2">
-        <v>81.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>81.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-18.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1804727192401149</v>
+        <v>0.1566731141199226</v>
       </c>
       <c r="AI2">
-        <v>0.1735344095157179</v>
+        <v>0.1340857787810384</v>
       </c>
       <c r="AJ2">
-        <v>-0.05158730158730159</v>
+        <v>0.1566731141199226</v>
       </c>
       <c r="AK2">
-        <v>-0.04906983014289566</v>
+        <v>0.1340857787810384</v>
       </c>
       <c r="AL2">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="AM2">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="AN2">
-        <v>0.9294653014789533</v>
+        <v>0.8830525272547075</v>
       </c>
       <c r="AO2">
-        <v>25.67823343848581</v>
+        <v>28.59237536656891</v>
       </c>
       <c r="AP2">
-        <v>-0.2070534698521047</v>
+        <v>0.8830525272547075</v>
       </c>
       <c r="AQ2">
-        <v>25.67823343848581</v>
+        <v>28.59237536656891</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.05980000000000001</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="E3">
-        <v>0.16</v>
+        <v>0.121</v>
       </c>
       <c r="G3">
-        <v>0.1746737841043891</v>
+        <v>0.1165672326755392</v>
       </c>
       <c r="H3">
-        <v>0.1746737841043891</v>
+        <v>0.1165672326755392</v>
       </c>
       <c r="I3">
-        <v>0.120699881376038</v>
+        <v>0.111863240018357</v>
       </c>
       <c r="J3">
-        <v>0.0989646536952955</v>
+        <v>0.08915234463666036</v>
       </c>
       <c r="K3">
-        <v>64</v>
+        <v>73.7</v>
       </c>
       <c r="L3">
-        <v>0.09489916963226572</v>
+        <v>0.08455713630105553</v>
       </c>
       <c r="M3">
-        <v>22.8</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.061455525606469</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.35625</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>22.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.061455525606469</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.35625</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>99.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.2692722371967655</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1121036959187248</v>
+        <v>0.1896063802418318</v>
       </c>
       <c r="X3">
-        <v>0.1416959172781294</v>
+        <v>0.1170478436518125</v>
       </c>
       <c r="Y3">
-        <v>-0.02959222135940459</v>
+        <v>0.07255853659001923</v>
       </c>
       <c r="Z3">
-        <v>1.219309347315133</v>
+        <v>2.352496626180837</v>
       </c>
       <c r="AA3">
-        <v>0.1206685273044789</v>
+        <v>0.2097305899738547</v>
       </c>
       <c r="AB3">
-        <v>0.1251823828519256</v>
+        <v>0.1060832382678796</v>
       </c>
       <c r="AC3">
-        <v>-0.004513855547446752</v>
+        <v>0.1036473517059751</v>
       </c>
       <c r="AD3">
-        <v>81.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>81.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>-18.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1804727192401149</v>
+        <v>0.1566731141199226</v>
       </c>
       <c r="AI3">
-        <v>0.1735344095157179</v>
+        <v>0.1340857787810384</v>
       </c>
       <c r="AJ3">
-        <v>-0.05158730158730159</v>
+        <v>0.1566731141199226</v>
       </c>
       <c r="AK3">
-        <v>-0.04906983014289566</v>
+        <v>0.1340857787810384</v>
       </c>
       <c r="AL3">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="AM3">
-        <v>3.17</v>
+        <v>3.41</v>
       </c>
       <c r="AN3">
-        <v>0.9294653014789533</v>
+        <v>0.8830525272547075</v>
       </c>
       <c r="AO3">
-        <v>25.67823343848581</v>
+        <v>28.59237536656891</v>
       </c>
       <c r="AP3">
-        <v>-0.2070534698521047</v>
+        <v>0.8830525272547075</v>
       </c>
       <c r="AQ3">
-        <v>25.67823343848581</v>
+        <v>28.59237536656891</v>
       </c>
     </row>
   </sheetData>
